--- a/sheets/S08A22P232.xlsx
+++ b/sheets/S08A22P232.xlsx
@@ -343,7 +343,7 @@
     <t>Hari Prakash</t>
   </si>
   <si>
-    <t>HR/03/15/0324416</t>
+    <t>HR/03/15/0324243</t>
   </si>
   <si>
     <t>Puran Chand</t>
@@ -634,7 +634,7 @@
     <t>HR/03/15/0324280</t>
   </si>
   <si>
-    <t>HR/03/15/0324243</t>
+    <t>HR/03/15/0324843</t>
   </si>
   <si>
     <t>Shish Pal</t>
